--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 22:00</t>
+    <t xml:space="preserve">2026-09-10 01:11</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-10 01:11</t>
+    <t xml:space="preserve">2026-09-12 22:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 22:24</t>
+    <t xml:space="preserve">2026-09-23 23:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 23:53</t>
+    <t xml:space="preserve">2026-10-02 15:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:53</t>
+    <t xml:space="preserve">2026-10-04 10:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_d_dep_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 10:35</t>
+    <t xml:space="preserve">2026-10-05 16:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1085,7 +1085,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>60.62</v>
+        <v>60.63</v>
       </c>
     </row>
     <row r="32">
